--- a/results/Benchmark Summary - resubmission.xlsx
+++ b/results/Benchmark Summary - resubmission.xlsx
@@ -211,7 +211,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,11 +294,20 @@
     <xf numFmtId="2" fontId="3" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -739,51 +748,51 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>78.37</v>
+        <v>78.39400000000001</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>85.98999999999999</v>
+        <v>85.996</v>
       </c>
       <c r="F3" s="35" t="n">
         <v>85.86</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>78.37</v>
+        <v>78.39400000000001</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>82.48999999999999</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>74.25</v>
+        <v>74.248</v>
       </c>
       <c r="J3" s="35" t="n">
-        <v>56.96</v>
+        <v>57.016</v>
       </c>
       <c r="K3" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L3" s="30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.3</v>
+      <c r="L3" s="36" t="n">
+        <v>1.123067</v>
+      </c>
+      <c r="M3" s="37" t="n">
+        <v>1.555178</v>
+      </c>
+      <c r="N3" s="38" t="n">
+        <v>1.746139</v>
+      </c>
+      <c r="O3" s="38" t="n">
+        <v>1.123067</v>
+      </c>
+      <c r="P3" s="38" t="n">
+        <v>2.285038</v>
+      </c>
+      <c r="Q3" s="38" t="n">
+        <v>2.114124</v>
+      </c>
+      <c r="R3" s="38" t="n">
+        <v>2.258723</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -827,8 +836,8 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="36" t="n"/>
-      <c r="B5" s="36" t="n"/>
+      <c r="A5" s="39" t="n"/>
+      <c r="B5" s="39" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>mAHTPred</t>
@@ -915,51 +924,51 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>85.86</v>
+        <v>85.864</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>94.64</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>94.31</v>
+        <v>94.306</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>85.86</v>
+        <v>85.864</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>86.47</v>
+        <v>86.46599999999999</v>
       </c>
       <c r="I7" s="35" t="n">
-        <v>85.26000000000001</v>
+        <v>85.262</v>
       </c>
       <c r="J7" s="35" t="n">
-        <v>71.95</v>
+        <v>71.952</v>
       </c>
       <c r="K7" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.91</v>
+      <c r="L7" s="38" t="n">
+        <v>1.318173</v>
+      </c>
+      <c r="M7" s="38" t="n">
+        <v>0.551226</v>
+      </c>
+      <c r="N7" s="38" t="n">
+        <v>1.122199</v>
+      </c>
+      <c r="O7" s="38" t="n">
+        <v>1.318173</v>
+      </c>
+      <c r="P7" s="38" t="n">
+        <v>5.183891</v>
+      </c>
+      <c r="Q7" s="38" t="n">
+        <v>3.591987</v>
+      </c>
+      <c r="R7" s="38" t="n">
+        <v>2.914021</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1003,8 +1012,8 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
+      <c r="A9" s="39" t="n"/>
+      <c r="B9" s="39" t="n"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>iDPPIV-SCM</t>
@@ -1130,51 +1139,51 @@
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>87.97</v>
+        <v>87.968</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>95.97</v>
+        <v>95.958</v>
       </c>
       <c r="F12" s="35" t="n">
-        <v>96.23</v>
+        <v>96.22799999999999</v>
       </c>
       <c r="G12" s="35" t="n">
-        <v>87.97</v>
+        <v>87.968</v>
       </c>
       <c r="H12" s="35" t="n">
-        <v>92.5</v>
+        <v>92.498</v>
       </c>
       <c r="I12" s="35" t="n">
-        <v>83.44</v>
+        <v>83.438</v>
       </c>
       <c r="J12" s="35" t="n">
-        <v>76.39</v>
+        <v>76.38800000000001</v>
       </c>
       <c r="K12" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.84</v>
+      <c r="L12" s="38" t="n">
+        <v>1.30519</v>
+      </c>
+      <c r="M12" s="38" t="n">
+        <v>0.191494</v>
+      </c>
+      <c r="N12" s="38" t="n">
+        <v>0.284201</v>
+      </c>
+      <c r="O12" s="38" t="n">
+        <v>1.30519</v>
+      </c>
+      <c r="P12" s="38" t="n">
+        <v>4.190951</v>
+      </c>
+      <c r="Q12" s="38" t="n">
+        <v>2.615162</v>
+      </c>
+      <c r="R12" s="38" t="n">
+        <v>2.83514</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1218,8 +1227,8 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
+      <c r="A14" s="39" t="n"/>
+      <c r="B14" s="39" t="n"/>
       <c r="C14" s="27" t="inlineStr">
         <is>
           <t>iBitter-Fuse</t>
@@ -1309,48 +1318,48 @@
         <v>85.17</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>92.73</v>
+        <v>92.72799999999999</v>
       </c>
       <c r="F16" s="35" t="n">
         <v>84.88</v>
       </c>
       <c r="G16" s="35" t="n">
-        <v>82.03</v>
+        <v>82.032</v>
       </c>
       <c r="H16" s="35" t="n">
-        <v>73.56999999999999</v>
+        <v>73.572</v>
       </c>
       <c r="I16" s="35" t="n">
         <v>90.48999999999999</v>
       </c>
       <c r="J16" s="35" t="n">
-        <v>65.23</v>
+        <v>65.224</v>
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.04</v>
+      <c r="L16" s="38" t="n">
+        <v>1.464906</v>
+      </c>
+      <c r="M16" s="38" t="n">
+        <v>0.88869</v>
+      </c>
+      <c r="N16" s="38" t="n">
+        <v>2.335969</v>
+      </c>
+      <c r="O16" s="38" t="n">
+        <v>1.123441</v>
+      </c>
+      <c r="P16" s="38" t="n">
+        <v>1.95537</v>
+      </c>
+      <c r="Q16" s="38" t="n">
+        <v>2.428806</v>
+      </c>
+      <c r="R16" s="38" t="n">
+        <v>3.047643</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1431,8 +1440,8 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
+      <c r="A19" s="39" t="n"/>
+      <c r="B19" s="39" t="n"/>
       <c r="C19" s="27" t="inlineStr">
         <is>
           <t>iUmami-SCM</t>
@@ -1522,19 +1531,19 @@
         <v>97.03</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>98.12</v>
+        <v>98.122</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>95.28</v>
+        <v>95.276</v>
       </c>
       <c r="G21" s="35" t="n">
-        <v>96.62</v>
+        <v>96.61799999999999</v>
       </c>
       <c r="H21" s="35" t="n">
-        <v>95.65000000000001</v>
+        <v>95.636</v>
       </c>
       <c r="I21" s="35" t="n">
-        <v>97.59</v>
+        <v>97.596</v>
       </c>
       <c r="J21" s="35" t="n">
         <v>92.83</v>
@@ -1544,26 +1553,26 @@
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.6899999999999999</v>
+      <c r="L21" s="38" t="n">
+        <v>0.309112</v>
+      </c>
+      <c r="M21" s="38" t="n">
+        <v>0.272433</v>
+      </c>
+      <c r="N21" s="38" t="n">
+        <v>1.905277</v>
+      </c>
+      <c r="O21" s="38" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="P21" s="38" t="n">
+        <v>1.163628</v>
+      </c>
+      <c r="Q21" s="38" t="n">
+        <v>0.794185</v>
+      </c>
+      <c r="R21" s="38" t="n">
+        <v>0.690109</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -1650,8 +1659,8 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="36" t="n"/>
+      <c r="A24" s="39" t="n"/>
+      <c r="B24" s="39" t="n"/>
       <c r="C24" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep-FL</t>
@@ -1736,51 +1745,51 @@
         </is>
       </c>
       <c r="D26" s="35" t="n">
-        <v>97.91</v>
+        <v>97.916</v>
       </c>
       <c r="E26" s="35" t="n">
-        <v>99.68000000000001</v>
+        <v>99.69199999999999</v>
       </c>
       <c r="F26" s="35" t="n">
-        <v>98.76000000000001</v>
+        <v>98.758</v>
       </c>
       <c r="G26" s="35" t="n">
-        <v>93.93000000000001</v>
+        <v>93.928</v>
       </c>
       <c r="H26" s="35" t="n">
-        <v>87.86</v>
+        <v>87.858</v>
       </c>
       <c r="I26" s="35" t="n">
         <v>100</v>
       </c>
       <c r="J26" s="35" t="n">
-        <v>92.56999999999999</v>
+        <v>92.572</v>
       </c>
       <c r="K26" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="L26" s="38" t="n">
+        <v>0.334111</v>
+      </c>
+      <c r="M26" s="38" t="n">
+        <v>0.178522</v>
+      </c>
+      <c r="N26" s="38" t="n">
+        <v>0.569271</v>
+      </c>
+      <c r="O26" s="38" t="n">
+        <v>0.974946</v>
+      </c>
+      <c r="P26" s="38" t="n">
+        <v>1.960847</v>
+      </c>
+      <c r="Q26" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.21</v>
+      <c r="R26" s="38" t="n">
+        <v>1.215944</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -1862,7 +1871,7 @@
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="34" t="n"/>
-      <c r="B29" s="36" t="n"/>
+      <c r="B29" s="39" t="n"/>
       <c r="C29" s="27" t="inlineStr">
         <is>
           <t>iAMAP-SCM</t>
@@ -1954,42 +1963,42 @@
         <v>80.5</v>
       </c>
       <c r="G31" s="35" t="n">
-        <v>82.58</v>
+        <v>82.578</v>
       </c>
       <c r="H31" s="35" t="n">
-        <v>65.70999999999999</v>
+        <v>65.71599999999999</v>
       </c>
       <c r="I31" s="35" t="n">
         <v>99.44</v>
       </c>
       <c r="J31" s="35" t="n">
-        <v>74.98999999999999</v>
+        <v>74.98399999999999</v>
       </c>
       <c r="K31" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.84</v>
+      <c r="L31" s="38" t="n">
+        <v>0.269444</v>
+      </c>
+      <c r="M31" s="38" t="n">
+        <v>1.65159</v>
+      </c>
+      <c r="N31" s="38" t="n">
+        <v>1.453135</v>
+      </c>
+      <c r="O31" s="38" t="n">
+        <v>2.005286</v>
+      </c>
+      <c r="P31" s="38" t="n">
+        <v>4.073497</v>
+      </c>
+      <c r="Q31" s="38" t="n">
+        <v>0.209643</v>
+      </c>
+      <c r="R31" s="38" t="n">
+        <v>2.835891</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2070,8 +2079,8 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="36" t="n"/>
+      <c r="A34" s="39" t="n"/>
+      <c r="B34" s="39" t="n"/>
       <c r="C34" s="27" t="inlineStr">
         <is>
           <t>iAMAP-SCM</t>
@@ -2201,7 +2210,7 @@
         <v>98.3</v>
       </c>
       <c r="F37" s="35" t="n">
-        <v>98.42</v>
+        <v>98.416</v>
       </c>
       <c r="G37" s="35" t="n">
         <v>90</v>
@@ -2220,26 +2229,26 @@
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P37" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7.07</v>
+      <c r="L37" s="38" t="n">
+        <v>3.535534</v>
+      </c>
+      <c r="M37" s="38" t="n">
+        <v>0.908295</v>
+      </c>
+      <c r="N37" s="38" t="n">
+        <v>0.81779</v>
+      </c>
+      <c r="O37" s="38" t="n">
+        <v>3.535534</v>
+      </c>
+      <c r="P37" s="38" t="n">
+        <v>4.472136</v>
+      </c>
+      <c r="Q37" s="38" t="n">
+        <v>4.472136</v>
+      </c>
+      <c r="R37" s="38" t="n">
+        <v>7.074461</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -2283,8 +2292,8 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="36" t="n"/>
-      <c r="B39" s="36" t="n"/>
+      <c r="A39" s="39" t="n"/>
+      <c r="B39" s="39" t="n"/>
       <c r="C39" s="27" t="inlineStr">
         <is>
           <t>iQSP</t>
@@ -2416,51 +2425,51 @@
         </is>
       </c>
       <c r="D42" s="35" t="n">
-        <v>92.89</v>
+        <v>92.886</v>
       </c>
       <c r="E42" s="35" t="n">
-        <v>96.81</v>
+        <v>96.812</v>
       </c>
       <c r="F42" s="35" t="n">
         <v>96.93000000000001</v>
       </c>
       <c r="G42" s="35" t="n">
-        <v>92.89</v>
+        <v>92.886</v>
       </c>
       <c r="H42" s="35" t="n">
         <v>91.34</v>
       </c>
       <c r="I42" s="35" t="n">
-        <v>94.43000000000001</v>
+        <v>94.434</v>
       </c>
       <c r="J42" s="35" t="n">
-        <v>85.81999999999999</v>
+        <v>85.816</v>
       </c>
       <c r="K42" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.4</v>
+      <c r="L42" s="38" t="n">
+        <v>0.698412</v>
+      </c>
+      <c r="M42" s="38" t="n">
+        <v>0.655034</v>
+      </c>
+      <c r="N42" s="38" t="n">
+        <v>0.97085</v>
+      </c>
+      <c r="O42" s="38" t="n">
+        <v>0.698412</v>
+      </c>
+      <c r="P42" s="38" t="n">
+        <v>0.6730159999999999</v>
+      </c>
+      <c r="Q42" s="38" t="n">
+        <v>0.993745</v>
+      </c>
+      <c r="R42" s="38" t="n">
+        <v>1.402794</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -2505,7 +2514,7 @@
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="34" t="n"/>
-      <c r="B44" s="36" t="n"/>
+      <c r="B44" s="39" t="n"/>
       <c r="C44" s="27" t="inlineStr">
         <is>
           <t>iACP-FSCM</t>
@@ -2629,22 +2638,22 @@
         </is>
       </c>
       <c r="D47" s="35" t="n">
-        <v>73.59999999999999</v>
+        <v>73.604</v>
       </c>
       <c r="E47" s="35" t="n">
-        <v>81.48</v>
+        <v>81.486</v>
       </c>
       <c r="F47" s="35" t="n">
         <v>82.12</v>
       </c>
       <c r="G47" s="35" t="n">
-        <v>73.59999999999999</v>
+        <v>73.604</v>
       </c>
       <c r="H47" s="35" t="n">
-        <v>79.88</v>
+        <v>79.884</v>
       </c>
       <c r="I47" s="35" t="n">
-        <v>67.33</v>
+        <v>67.32599999999999</v>
       </c>
       <c r="J47" s="35" t="n">
         <v>47.66</v>
@@ -2654,26 +2663,26 @@
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="R47" t="n">
-        <v>2.53</v>
+      <c r="L47" s="38" t="n">
+        <v>1.258344</v>
+      </c>
+      <c r="M47" s="38" t="n">
+        <v>1.236883</v>
+      </c>
+      <c r="N47" s="38" t="n">
+        <v>1.848229</v>
+      </c>
+      <c r="O47" s="38" t="n">
+        <v>1.258344</v>
+      </c>
+      <c r="P47" s="38" t="n">
+        <v>3.304063</v>
+      </c>
+      <c r="Q47" s="38" t="n">
+        <v>3.273642</v>
+      </c>
+      <c r="R47" s="38" t="n">
+        <v>2.528191</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -2717,8 +2726,8 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="36" t="n"/>
-      <c r="B49" s="36" t="n"/>
+      <c r="A49" s="39" t="n"/>
+      <c r="B49" s="39" t="n"/>
       <c r="C49" s="27" t="inlineStr">
         <is>
           <t>iACP-FSCM</t>
@@ -2803,51 +2812,51 @@
         </is>
       </c>
       <c r="D51" s="35" t="n">
-        <v>99.09999999999999</v>
+        <v>99.092</v>
       </c>
       <c r="E51" s="35" t="n">
-        <v>98.69</v>
+        <v>98.702</v>
       </c>
       <c r="F51" s="35" t="n">
-        <v>97.97</v>
+        <v>97.968</v>
       </c>
       <c r="G51" s="35" t="n">
-        <v>98.09999999999999</v>
+        <v>98.098</v>
       </c>
       <c r="H51" s="35" t="n">
         <v>96.67</v>
       </c>
       <c r="I51" s="35" t="n">
-        <v>99.53</v>
+        <v>99.52800000000001</v>
       </c>
       <c r="J51" s="35" t="n">
-        <v>96.47</v>
+        <v>96.462</v>
       </c>
       <c r="K51" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="P51" t="n">
+      <c r="L51" s="38" t="n">
+        <v>0.228079</v>
+      </c>
+      <c r="M51" s="38" t="n">
+        <v>0.867796</v>
+      </c>
+      <c r="N51" s="38" t="n">
+        <v>0.69751</v>
+      </c>
+      <c r="O51" s="38" t="n">
+        <v>0.129692</v>
+      </c>
+      <c r="P51" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.87</v>
+      <c r="Q51" s="38" t="n">
+        <v>0.263856</v>
+      </c>
+      <c r="R51" s="38" t="n">
+        <v>0.876539</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -2928,8 +2937,8 @@
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="36" t="n"/>
-      <c r="B54" s="36" t="n"/>
+      <c r="A54" s="39" t="n"/>
+      <c r="B54" s="39" t="n"/>
       <c r="C54" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep-FL</t>
@@ -3056,48 +3065,48 @@
         <v>74.01000000000001</v>
       </c>
       <c r="E57" s="35" t="n">
-        <v>79.59</v>
+        <v>79.574</v>
       </c>
       <c r="F57" s="35" t="n">
-        <v>86.03</v>
+        <v>86.026</v>
       </c>
       <c r="G57" s="35" t="n">
         <v>70.08</v>
       </c>
       <c r="H57" s="35" t="n">
-        <v>86.56</v>
+        <v>86.556</v>
       </c>
       <c r="I57" s="35" t="n">
-        <v>53.6</v>
+        <v>53.598</v>
       </c>
       <c r="J57" s="35" t="n">
-        <v>43.38</v>
+        <v>43.372</v>
       </c>
       <c r="K57" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P57" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="R57" t="n">
-        <v>4.91</v>
+      <c r="L57" s="38" t="n">
+        <v>2.312228</v>
+      </c>
+      <c r="M57" s="38" t="n">
+        <v>1.94257</v>
+      </c>
+      <c r="N57" s="38" t="n">
+        <v>1.54484</v>
+      </c>
+      <c r="O57" s="38" t="n">
+        <v>2.234491</v>
+      </c>
+      <c r="P57" s="38" t="n">
+        <v>5.070614</v>
+      </c>
+      <c r="Q57" s="38" t="n">
+        <v>5.916005</v>
+      </c>
+      <c r="R57" s="38" t="n">
+        <v>4.911107</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -3141,8 +3150,8 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="36" t="n"/>
-      <c r="B59" s="36" t="n"/>
+      <c r="A59" s="39" t="n"/>
+      <c r="B59" s="39" t="n"/>
       <c r="C59" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep-FL</t>
@@ -3266,51 +3275,51 @@
         </is>
       </c>
       <c r="D62" s="35" t="n">
-        <v>80.53</v>
+        <v>80.52800000000001</v>
       </c>
       <c r="E62" s="35" t="n">
-        <v>92.52</v>
+        <v>92.518</v>
       </c>
       <c r="F62" s="35" t="n">
-        <v>93.53</v>
+        <v>93.52800000000001</v>
       </c>
       <c r="G62" s="35" t="n">
-        <v>80.53</v>
+        <v>80.52800000000001</v>
       </c>
       <c r="H62" s="35" t="n">
-        <v>66.31999999999999</v>
+        <v>66.316</v>
       </c>
       <c r="I62" s="35" t="n">
         <v>94.73999999999999</v>
       </c>
       <c r="J62" s="35" t="n">
-        <v>63.75</v>
+        <v>63.748</v>
       </c>
       <c r="K62" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="N62" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O62" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="P62" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="Q62" t="n">
+      <c r="L62" s="38" t="n">
+        <v>3.988592</v>
+      </c>
+      <c r="M62" s="38" t="n">
+        <v>2.926315</v>
+      </c>
+      <c r="N62" s="38" t="n">
+        <v>2.051114</v>
+      </c>
+      <c r="O62" s="38" t="n">
+        <v>3.988592</v>
+      </c>
+      <c r="P62" s="38" t="n">
+        <v>7.983779</v>
+      </c>
+      <c r="Q62" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="R62" t="n">
-        <v>6.84</v>
+      <c r="R62" s="38" t="n">
+        <v>6.83741</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -3319,8 +3328,8 @@
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="36" t="n"/>
-      <c r="B63" s="36" t="n"/>
+      <c r="A63" s="39" t="n"/>
+      <c r="B63" s="39" t="n"/>
       <c r="C63" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -3442,51 +3451,51 @@
         </is>
       </c>
       <c r="D66" s="35" t="n">
-        <v>67.83</v>
+        <v>67.828</v>
       </c>
       <c r="E66" s="35" t="n">
-        <v>81.83</v>
+        <v>81.786</v>
       </c>
       <c r="F66" s="35" t="n">
-        <v>84.70999999999999</v>
+        <v>84.714</v>
       </c>
       <c r="G66" s="35" t="n">
-        <v>67.83</v>
+        <v>67.828</v>
       </c>
       <c r="H66" s="35" t="n">
         <v>40.87</v>
       </c>
       <c r="I66" s="35" t="n">
-        <v>94.78</v>
+        <v>94.782</v>
       </c>
       <c r="J66" s="35" t="n">
-        <v>42.24</v>
+        <v>42.242</v>
       </c>
       <c r="K66" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M66" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="N66" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="O66" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="P66" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="R66" t="n">
-        <v>6.16</v>
+      <c r="L66" s="38" t="n">
+        <v>3.132103</v>
+      </c>
+      <c r="M66" s="38" t="n">
+        <v>6.324139</v>
+      </c>
+      <c r="N66" s="38" t="n">
+        <v>4.02126</v>
+      </c>
+      <c r="O66" s="38" t="n">
+        <v>3.132103</v>
+      </c>
+      <c r="P66" s="38" t="n">
+        <v>5.191695</v>
+      </c>
+      <c r="Q66" s="38" t="n">
+        <v>1.188558</v>
+      </c>
+      <c r="R66" s="38" t="n">
+        <v>6.155999</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -3495,8 +3504,8 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="36" t="n"/>
-      <c r="B67" s="36" t="n"/>
+      <c r="A67" s="39" t="n"/>
+      <c r="B67" s="39" t="n"/>
       <c r="C67" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -3657,51 +3666,51 @@
         </is>
       </c>
       <c r="D71" s="35" t="n">
-        <v>88.7</v>
+        <v>88.724</v>
       </c>
       <c r="E71" s="35" t="n">
-        <v>94.94</v>
+        <v>94.944</v>
       </c>
       <c r="F71" s="35" t="n">
-        <v>95.22</v>
+        <v>95.218</v>
       </c>
       <c r="G71" s="35" t="n">
-        <v>88.7</v>
+        <v>88.724</v>
       </c>
       <c r="H71" s="35" t="n">
-        <v>86.72</v>
+        <v>86.762</v>
       </c>
       <c r="I71" s="35" t="n">
         <v>90.68000000000001</v>
       </c>
       <c r="J71" s="35" t="n">
-        <v>77.55</v>
+        <v>77.592</v>
       </c>
       <c r="K71" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="P71" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.82</v>
+      <c r="L71" s="38" t="n">
+        <v>0.511107</v>
+      </c>
+      <c r="M71" s="38" t="n">
+        <v>0.333587</v>
+      </c>
+      <c r="N71" s="38" t="n">
+        <v>0.354429</v>
+      </c>
+      <c r="O71" s="38" t="n">
+        <v>0.511107</v>
+      </c>
+      <c r="P71" s="38" t="n">
+        <v>3.105989</v>
+      </c>
+      <c r="Q71" s="38" t="n">
+        <v>2.331105</v>
+      </c>
+      <c r="R71" s="38" t="n">
+        <v>0.855552</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -3710,8 +3719,8 @@
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="36" t="n"/>
-      <c r="B72" s="36" t="n"/>
+      <c r="A72" s="39" t="n"/>
+      <c r="B72" s="39" t="n"/>
       <c r="C72" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -3833,7 +3842,7 @@
         </is>
       </c>
       <c r="D75" s="35" t="n">
-        <v>94.53</v>
+        <v>94.52</v>
       </c>
       <c r="E75" s="35" t="n">
         <v>97.29000000000001</v>
@@ -3842,42 +3851,42 @@
         <v>97.23999999999999</v>
       </c>
       <c r="G75" s="35" t="n">
-        <v>94.53</v>
+        <v>94.52</v>
       </c>
       <c r="H75" s="35" t="n">
-        <v>93.48999999999999</v>
+        <v>93.464</v>
       </c>
       <c r="I75" s="35" t="n">
-        <v>95.58</v>
+        <v>95.57599999999999</v>
       </c>
       <c r="J75" s="35" t="n">
-        <v>89.08</v>
+        <v>89.062</v>
       </c>
       <c r="K75" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.61</v>
+      <c r="L75" s="38" t="n">
+        <v>0.298998</v>
+      </c>
+      <c r="M75" s="38" t="n">
+        <v>0.177904</v>
+      </c>
+      <c r="N75" s="38" t="n">
+        <v>0.402182</v>
+      </c>
+      <c r="O75" s="38" t="n">
+        <v>0.298998</v>
+      </c>
+      <c r="P75" s="38" t="n">
+        <v>0.306072</v>
+      </c>
+      <c r="Q75" s="38" t="n">
+        <v>0.633467</v>
+      </c>
+      <c r="R75" s="38" t="n">
+        <v>0.60545</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -3886,8 +3895,8 @@
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="36" t="n"/>
-      <c r="B76" s="36" t="n"/>
+      <c r="A76" s="39" t="n"/>
+      <c r="B76" s="39" t="n"/>
       <c r="C76" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4009,51 +4018,51 @@
         </is>
       </c>
       <c r="D79" s="35" t="n">
-        <v>94.33</v>
+        <v>94.372</v>
       </c>
       <c r="E79" s="35" t="n">
-        <v>98.91</v>
+        <v>98.914</v>
       </c>
       <c r="F79" s="35" t="n">
         <v>99.04000000000001</v>
       </c>
       <c r="G79" s="35" t="n">
-        <v>94.33</v>
+        <v>94.372</v>
       </c>
       <c r="H79" s="35" t="n">
-        <v>93.40000000000001</v>
+        <v>93.39400000000001</v>
       </c>
       <c r="I79" s="35" t="n">
-        <v>95.26000000000001</v>
+        <v>95.346</v>
       </c>
       <c r="J79" s="35" t="n">
-        <v>88.68000000000001</v>
+        <v>88.776</v>
       </c>
       <c r="K79" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.09</v>
+      <c r="L79" s="38" t="n">
+        <v>0.446061</v>
+      </c>
+      <c r="M79" s="38" t="n">
+        <v>0.220635</v>
+      </c>
+      <c r="N79" s="38" t="n">
+        <v>0.152971</v>
+      </c>
+      <c r="O79" s="38" t="n">
+        <v>0.446061</v>
+      </c>
+      <c r="P79" s="38" t="n">
+        <v>0.608589</v>
+      </c>
+      <c r="Q79" s="38" t="n">
+        <v>1.471251</v>
+      </c>
+      <c r="R79" s="38" t="n">
+        <v>0.917104</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -4062,8 +4071,8 @@
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="36" t="n"/>
-      <c r="B80" s="36" t="n"/>
+      <c r="A80" s="39" t="n"/>
+      <c r="B80" s="39" t="n"/>
       <c r="C80" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4185,51 +4194,51 @@
         </is>
       </c>
       <c r="D83" s="35" t="n">
-        <v>83.95999999999999</v>
+        <v>83.996</v>
       </c>
       <c r="E83" s="35" t="n">
-        <v>91.55</v>
+        <v>91.55200000000001</v>
       </c>
       <c r="F83" s="35" t="n">
-        <v>92</v>
+        <v>91.996</v>
       </c>
       <c r="G83" s="35" t="n">
-        <v>83.95999999999999</v>
+        <v>83.996</v>
       </c>
       <c r="H83" s="35" t="n">
         <v>82.44</v>
       </c>
       <c r="I83" s="35" t="n">
-        <v>85.48999999999999</v>
+        <v>85.554</v>
       </c>
       <c r="J83" s="35" t="n">
-        <v>68.03</v>
+        <v>68.098</v>
       </c>
       <c r="K83" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1.86</v>
+      <c r="L83" s="38" t="n">
+        <v>0.870506</v>
+      </c>
+      <c r="M83" s="38" t="n">
+        <v>0.459532</v>
+      </c>
+      <c r="N83" s="38" t="n">
+        <v>0.76745</v>
+      </c>
+      <c r="O83" s="38" t="n">
+        <v>0.870506</v>
+      </c>
+      <c r="P83" s="38" t="n">
+        <v>1.770763</v>
+      </c>
+      <c r="Q83" s="38" t="n">
+        <v>3.311696</v>
+      </c>
+      <c r="R83" s="38" t="n">
+        <v>1.828858</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -4238,8 +4247,8 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="36" t="n"/>
-      <c r="B84" s="36" t="n"/>
+      <c r="A84" s="39" t="n"/>
+      <c r="B84" s="39" t="n"/>
       <c r="C84" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4361,51 +4370,51 @@
         </is>
       </c>
       <c r="D87" s="35" t="n">
-        <v>92.48</v>
+        <v>92.482</v>
       </c>
       <c r="E87" s="35" t="n">
-        <v>96.14</v>
+        <v>96.13800000000001</v>
       </c>
       <c r="F87" s="35" t="n">
-        <v>95.44</v>
+        <v>95.444</v>
       </c>
       <c r="G87" s="35" t="n">
         <v>92.43000000000001</v>
       </c>
       <c r="H87" s="35" t="n">
-        <v>91.67</v>
+        <v>91.67400000000001</v>
       </c>
       <c r="I87" s="35" t="n">
-        <v>93.18000000000001</v>
+        <v>93.184</v>
       </c>
       <c r="J87" s="35" t="n">
-        <v>84.92</v>
+        <v>84.91800000000001</v>
       </c>
       <c r="K87" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.6</v>
+      <c r="L87" s="38" t="n">
+        <v>0.289258</v>
+      </c>
+      <c r="M87" s="38" t="n">
+        <v>0.465478</v>
+      </c>
+      <c r="N87" s="38" t="n">
+        <v>0.770409</v>
+      </c>
+      <c r="O87" s="38" t="n">
+        <v>0.329924</v>
+      </c>
+      <c r="P87" s="38" t="n">
+        <v>1.83477</v>
+      </c>
+      <c r="Q87" s="38" t="n">
+        <v>1.51188</v>
+      </c>
+      <c r="R87" s="38" t="n">
+        <v>0.601224</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -4414,8 +4423,8 @@
       </c>
     </row>
     <row r="88" thickBot="1">
-      <c r="A88" s="36" t="n"/>
-      <c r="B88" s="36" t="n"/>
+      <c r="A88" s="39" t="n"/>
+      <c r="B88" s="39" t="n"/>
       <c r="C88" s="27" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4462,25 +4471,25 @@
           <t>MTL-PepPred</t>
         </is>
       </c>
-      <c r="D89" s="37" t="n">
+      <c r="D89" s="40" t="n">
         <v>75.09</v>
       </c>
-      <c r="E89" s="38" t="n">
-        <v>82.95999999999999</v>
-      </c>
-      <c r="F89" s="38" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="G89" s="38" t="n">
-        <v>75.27</v>
-      </c>
-      <c r="H89" s="38" t="n">
-        <v>80</v>
-      </c>
-      <c r="I89" s="38" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="J89" s="38" t="n">
+      <c r="E89" s="41" t="n">
+        <v>82.968</v>
+      </c>
+      <c r="F89" s="41" t="n">
+        <v>81.604</v>
+      </c>
+      <c r="G89" s="41" t="n">
+        <v>75.274</v>
+      </c>
+      <c r="H89" s="41" t="n">
+        <v>80.002</v>
+      </c>
+      <c r="I89" s="41" t="n">
+        <v>70.548</v>
+      </c>
+      <c r="J89" s="41" t="n">
         <v>50.83</v>
       </c>
       <c r="K89" s="8" t="inlineStr">
@@ -4488,26 +4497,26 @@
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="O89" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P89" s="2" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>2.24</v>
+      <c r="L89" s="42" t="n">
+        <v>1.307077</v>
+      </c>
+      <c r="M89" s="43" t="n">
+        <v>0.530726</v>
+      </c>
+      <c r="N89" s="43" t="n">
+        <v>0.591295</v>
+      </c>
+      <c r="O89" s="43" t="n">
+        <v>1.181537</v>
+      </c>
+      <c r="P89" s="43" t="n">
+        <v>4.022912</v>
+      </c>
+      <c r="Q89" s="43" t="n">
+        <v>5.498874</v>
+      </c>
+      <c r="R89" s="43" t="n">
+        <v>2.236649</v>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
@@ -4520,8 +4529,8 @@
       <c r="W89" s="2" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A90" s="36" t="n"/>
-      <c r="B90" s="36" t="n"/>
+      <c r="A90" s="39" t="n"/>
+      <c r="B90" s="39" t="n"/>
       <c r="C90" s="8" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4613,52 +4622,52 @@
           <t>MTL-PepPred</t>
         </is>
       </c>
-      <c r="D92" s="39" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="E92" s="39" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="F92" s="39" t="n">
-        <v>99.86</v>
-      </c>
-      <c r="G92" s="39" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="H92" s="39" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="I92" s="39" t="n">
-        <v>99.27</v>
-      </c>
-      <c r="J92" s="39" t="n">
-        <v>98.59</v>
+      <c r="D92" s="44" t="n">
+        <v>99.29600000000001</v>
+      </c>
+      <c r="E92" s="44" t="n">
+        <v>99.91200000000001</v>
+      </c>
+      <c r="F92" s="44" t="n">
+        <v>99.864</v>
+      </c>
+      <c r="G92" s="44" t="n">
+        <v>99.29600000000001</v>
+      </c>
+      <c r="H92" s="44" t="n">
+        <v>99.32599999999999</v>
+      </c>
+      <c r="I92" s="44" t="n">
+        <v>99.268</v>
+      </c>
+      <c r="J92" s="44" t="n">
+        <v>98.596</v>
       </c>
       <c r="K92" s="32" t="inlineStr">
         <is>
           <t>This work (mean of 5 seeds)</t>
         </is>
       </c>
-      <c r="L92" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.24</v>
+      <c r="L92" s="38" t="n">
+        <v>0.120748</v>
+      </c>
+      <c r="M92" s="38" t="n">
+        <v>0.067602</v>
+      </c>
+      <c r="N92" s="38" t="n">
+        <v>0.118448</v>
+      </c>
+      <c r="O92" s="38" t="n">
+        <v>0.120748</v>
+      </c>
+      <c r="P92" s="38" t="n">
+        <v>0.076681</v>
+      </c>
+      <c r="Q92" s="38" t="n">
+        <v>0.229281</v>
+      </c>
+      <c r="R92" s="38" t="n">
+        <v>0.246232</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -4667,8 +4676,8 @@
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="36" t="n"/>
-      <c r="B93" s="36" t="n"/>
+      <c r="A93" s="39" t="n"/>
+      <c r="B93" s="39" t="n"/>
       <c r="C93" s="25" t="inlineStr">
         <is>
           <t>UniDL4BioPep</t>
@@ -4811,7 +4820,7 @@
       </c>
       <c r="K1" s="33" t="inlineStr">
         <is>
-          <t>derived prevalence (pos/total)</t>
+          <t>prevalence (pos/total)</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>77.59</v>
+        <v>77.72</v>
       </c>
       <c r="E3" t="n">
         <v>84.62</v>
@@ -4878,16 +4887,16 @@
         <v>83.42</v>
       </c>
       <c r="G3" t="n">
-        <v>77.59</v>
+        <v>77.72</v>
       </c>
       <c r="H3" t="n">
-        <v>78.5</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>76.68000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>55.19</v>
+        <v>55.45</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
@@ -4950,7 +4959,7 @@
         <v>78.5</v>
       </c>
       <c r="E5" t="n">
-        <v>85.40000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F5" t="n">
         <v>85.78</v>
@@ -5067,7 +5076,7 @@
         <v>98.98999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>98.25</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>97.51000000000001</v>
@@ -5106,7 +5115,7 @@
         <v>99.5</v>
       </c>
       <c r="E9" t="n">
-        <v>98.17</v>
+        <v>98.19</v>
       </c>
       <c r="F9" t="n">
         <v>97.48999999999999</v>
@@ -5184,7 +5193,7 @@
         <v>98.98999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>97.75</v>
+        <v>97.81</v>
       </c>
       <c r="F11" t="n">
         <v>97.38</v>
@@ -5223,7 +5232,7 @@
         <v>68.48</v>
       </c>
       <c r="E12" t="n">
-        <v>85.75</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>87.40000000000001</v>
@@ -5262,7 +5271,7 @@
         <v>64.13</v>
       </c>
       <c r="E13" t="n">
-        <v>72.87</v>
+        <v>72.83</v>
       </c>
       <c r="F13" t="n">
         <v>79.34999999999999</v>
@@ -5301,7 +5310,7 @@
         <v>65.22</v>
       </c>
       <c r="E14" t="n">
-        <v>78.36</v>
+        <v>78.31</v>
       </c>
       <c r="F14" t="n">
         <v>81.62</v>
@@ -5379,7 +5388,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>83.29000000000001</v>
+        <v>83.22</v>
       </c>
       <c r="F16" t="n">
         <v>86.48999999999999</v>
@@ -5415,7 +5424,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>94.63</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>97.09999999999999</v>
@@ -5424,16 +5433,16 @@
         <v>96.78</v>
       </c>
       <c r="G17" t="n">
-        <v>94.63</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>93.09999999999999</v>
+        <v>92.98</v>
       </c>
       <c r="I17" t="n">
         <v>96.17</v>
       </c>
       <c r="J17" t="n">
-        <v>89.3</v>
+        <v>89.19</v>
       </c>
       <c r="K17" t="n">
         <v>0.5</v>
@@ -5457,7 +5466,7 @@
         <v>94.51000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>97.14</v>
+        <v>97.13</v>
       </c>
       <c r="F18" t="n">
         <v>97.11</v>
@@ -5613,7 +5622,7 @@
         <v>73.84</v>
       </c>
       <c r="E22" t="n">
-        <v>81.91</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>81.79000000000001</v>
@@ -5652,7 +5661,7 @@
         <v>75.58</v>
       </c>
       <c r="E23" t="n">
-        <v>83.42</v>
+        <v>83.45</v>
       </c>
       <c r="F23" t="n">
         <v>84.45999999999999</v>
@@ -5769,7 +5778,7 @@
         <v>72.67</v>
       </c>
       <c r="E26" t="n">
-        <v>80.98</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
         <v>79.48</v>
@@ -5808,7 +5817,7 @@
         <v>92.78</v>
       </c>
       <c r="E27" t="n">
-        <v>95.95999999999999</v>
+        <v>95.97</v>
       </c>
       <c r="F27" t="n">
         <v>95.44</v>
@@ -5886,7 +5895,7 @@
         <v>91.75</v>
       </c>
       <c r="E29" t="n">
-        <v>96.75</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>97.2</v>
@@ -5925,7 +5934,7 @@
         <v>93.04000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>97.48999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F30" t="n">
         <v>97.79000000000001</v>
@@ -6078,7 +6087,7 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>93.48999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="E34" t="n">
         <v>99.02</v>
@@ -6087,16 +6096,16 @@
         <v>99.13</v>
       </c>
       <c r="G34" t="n">
-        <v>93.48999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="H34" t="n">
         <v>94.42</v>
       </c>
       <c r="I34" t="n">
-        <v>92.56</v>
+        <v>93.02</v>
       </c>
       <c r="J34" t="n">
-        <v>86.98999999999999</v>
+        <v>87.45</v>
       </c>
       <c r="K34" t="n">
         <v>0.5</v>
@@ -6159,7 +6168,7 @@
         <v>94.19</v>
       </c>
       <c r="E36" t="n">
-        <v>99.22</v>
+        <v>99.23</v>
       </c>
       <c r="F36" t="n">
         <v>99.26000000000001</v>
@@ -6198,7 +6207,7 @@
         <v>97.36</v>
       </c>
       <c r="E37" t="n">
-        <v>93.43000000000001</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F37" t="n">
         <v>78.98999999999999</v>
@@ -6237,7 +6246,7 @@
         <v>97.58</v>
       </c>
       <c r="E38" t="n">
-        <v>91.73</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="F38" t="n">
         <v>81.65000000000001</v>
@@ -6276,7 +6285,7 @@
         <v>97.36</v>
       </c>
       <c r="E39" t="n">
-        <v>92.06</v>
+        <v>92.05</v>
       </c>
       <c r="F39" t="n">
         <v>82.39</v>
@@ -6315,7 +6324,7 @@
         <v>96.92</v>
       </c>
       <c r="E40" t="n">
-        <v>88.95999999999999</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="F40" t="n">
         <v>79.95999999999999</v>
@@ -6393,7 +6402,7 @@
         <v>97.55</v>
       </c>
       <c r="E42" t="n">
-        <v>99.73999999999999</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="F42" t="n">
         <v>98.91</v>
@@ -6432,7 +6441,7 @@
         <v>97.55</v>
       </c>
       <c r="E43" t="n">
-        <v>99.66</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="F43" t="n">
         <v>98.63</v>
@@ -6585,25 +6594,25 @@
         <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>96.56999999999999</v>
+        <v>96.56</v>
       </c>
       <c r="E47" t="n">
-        <v>97.93000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="F47" t="n">
         <v>93.25</v>
       </c>
       <c r="G47" t="n">
-        <v>96.52</v>
+        <v>96.5</v>
       </c>
       <c r="H47" t="n">
-        <v>96.40000000000001</v>
+        <v>96.36</v>
       </c>
       <c r="I47" t="n">
         <v>96.64</v>
       </c>
       <c r="J47" t="n">
-        <v>91.81</v>
+        <v>91.78</v>
       </c>
       <c r="K47" t="n">
         <v>0.2886</v>
@@ -6624,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>96.98</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="E48" t="n">
         <v>97.92</v>
@@ -6633,16 +6642,16 @@
         <v>94.61</v>
       </c>
       <c r="G48" t="n">
-        <v>96.73999999999999</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="H48" t="n">
         <v>96.17</v>
       </c>
       <c r="I48" t="n">
-        <v>97.31999999999999</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>92.73</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>0.2886</v>
@@ -6663,25 +6672,25 @@
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>97.38</v>
+        <v>97.36</v>
       </c>
       <c r="E49" t="n">
-        <v>98.45</v>
+        <v>98.44</v>
       </c>
       <c r="F49" t="n">
         <v>96.44</v>
       </c>
       <c r="G49" t="n">
-        <v>96.94</v>
+        <v>96.92</v>
       </c>
       <c r="H49" t="n">
-        <v>95.90000000000001</v>
+        <v>95.86</v>
       </c>
       <c r="I49" t="n">
         <v>97.97</v>
       </c>
       <c r="J49" t="n">
-        <v>93.63</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K49" t="n">
         <v>0.2886</v>
@@ -6783,7 +6792,7 @@
         <v>76.51000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>83.67</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F52" t="n">
         <v>81.14</v>
@@ -6861,7 +6870,7 @@
         <v>76.16</v>
       </c>
       <c r="E54" t="n">
-        <v>83.25</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="F54" t="n">
         <v>82.17</v>
@@ -6900,7 +6909,7 @@
         <v>73.31</v>
       </c>
       <c r="E55" t="n">
-        <v>82.28</v>
+        <v>82.27</v>
       </c>
       <c r="F55" t="n">
         <v>81.54000000000001</v>
@@ -6978,7 +6987,7 @@
         <v>83.95</v>
       </c>
       <c r="E57" t="n">
-        <v>91.06999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="F57" t="n">
         <v>91.56999999999999</v>
@@ -7014,7 +7023,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>82.5</v>
+        <v>82.58</v>
       </c>
       <c r="E58" t="n">
         <v>91.11</v>
@@ -7023,16 +7032,16 @@
         <v>91.83</v>
       </c>
       <c r="G58" t="n">
-        <v>82.5</v>
+        <v>82.58</v>
       </c>
       <c r="H58" t="n">
         <v>84.11</v>
       </c>
       <c r="I58" t="n">
-        <v>80.90000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="J58" t="n">
-        <v>65.04000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="K58" t="n">
         <v>0.5</v>
@@ -7056,7 +7065,7 @@
         <v>84.03</v>
       </c>
       <c r="E59" t="n">
-        <v>92.18000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="F59" t="n">
         <v>92.77</v>
@@ -7095,7 +7104,7 @@
         <v>84.75</v>
       </c>
       <c r="E60" t="n">
-        <v>91.70999999999999</v>
+        <v>91.72</v>
       </c>
       <c r="F60" t="n">
         <v>92.78</v>
@@ -7131,7 +7140,7 @@
         <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>84.59</v>
+        <v>84.67</v>
       </c>
       <c r="E61" t="n">
         <v>91.68000000000001</v>
@@ -7140,16 +7149,16 @@
         <v>91.03</v>
       </c>
       <c r="G61" t="n">
-        <v>84.59</v>
+        <v>84.67</v>
       </c>
       <c r="H61" t="n">
         <v>82.02</v>
       </c>
       <c r="I61" t="n">
-        <v>87.16</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>69.27</v>
+        <v>69.44</v>
       </c>
       <c r="K61" t="n">
         <v>0.5</v>
@@ -7368,7 +7377,7 @@
         <v>86.72</v>
       </c>
       <c r="E67" t="n">
-        <v>95.90000000000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="F67" t="n">
         <v>96.09999999999999</v>
@@ -7524,7 +7533,7 @@
         <v>89.84</v>
       </c>
       <c r="E71" t="n">
-        <v>95.8</v>
+        <v>95.78</v>
       </c>
       <c r="F71" t="n">
         <v>95.88</v>
@@ -7563,7 +7572,7 @@
         <v>84.59</v>
       </c>
       <c r="E72" t="n">
-        <v>94.05</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="F72" t="n">
         <v>92.48</v>
@@ -7641,7 +7650,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>94.54000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="F74" t="n">
         <v>94.55</v>
@@ -7680,7 +7689,7 @@
         <v>87.97</v>
       </c>
       <c r="E75" t="n">
-        <v>95.05</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F75" t="n">
         <v>94.97</v>
@@ -7719,7 +7728,7 @@
         <v>86.09</v>
       </c>
       <c r="E76" t="n">
-        <v>94.2</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="F76" t="n">
         <v>94.14</v>
@@ -7755,7 +7764,7 @@
         <v>42</v>
       </c>
       <c r="D77" t="n">
-        <v>89.06999999999999</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E77" t="n">
         <v>94.69</v>
@@ -7764,16 +7773,16 @@
         <v>94.86</v>
       </c>
       <c r="G77" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="H77" t="n">
         <v>89.06999999999999</v>
-      </c>
-      <c r="H77" t="n">
-        <v>88.87</v>
       </c>
       <c r="I77" t="n">
         <v>89.28</v>
       </c>
       <c r="J77" t="n">
-        <v>78.14</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K77" t="n">
         <v>0.5</v>
@@ -7797,7 +7806,7 @@
         <v>88.87</v>
       </c>
       <c r="E78" t="n">
-        <v>94.98</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="F78" t="n">
         <v>95.18000000000001</v>
@@ -8148,7 +8157,7 @@
         <v>99.12</v>
       </c>
       <c r="E87" t="n">
-        <v>99.83</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="F87" t="n">
         <v>99.73999999999999</v>
@@ -8382,7 +8391,7 @@
         <v>76.65000000000001</v>
       </c>
       <c r="E93" t="n">
-        <v>81.48999999999999</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="F93" t="n">
         <v>86.91</v>
@@ -8421,7 +8430,7 @@
         <v>71.56999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>78.09</v>
+        <v>78.08</v>
       </c>
       <c r="F94" t="n">
         <v>84.45</v>
@@ -8460,7 +8469,7 @@
         <v>75.13</v>
       </c>
       <c r="E95" t="n">
-        <v>81.41</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F95" t="n">
         <v>88.18000000000001</v>
@@ -8499,7 +8508,7 @@
         <v>71.56999999999999</v>
       </c>
       <c r="E96" t="n">
-        <v>77.15000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="F96" t="n">
         <v>84.76000000000001</v>
@@ -8538,7 +8547,7 @@
         <v>92.41</v>
       </c>
       <c r="E97" t="n">
-        <v>96.23</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="F97" t="n">
         <v>96.15000000000001</v>
@@ -8577,7 +8586,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>95.97</v>
+        <v>95.98</v>
       </c>
       <c r="F98" t="n">
         <v>95.44</v>
@@ -8616,7 +8625,7 @@
         <v>92.59</v>
       </c>
       <c r="E99" t="n">
-        <v>96.58</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F99" t="n">
         <v>95.22</v>
@@ -8655,7 +8664,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="E100" t="n">
-        <v>96.48</v>
+        <v>96.47</v>
       </c>
       <c r="F100" t="n">
         <v>96.13</v>
@@ -8921,48 +8930,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Built by Coding/update_benchmark_resubmission.py</t>
+          <t>Built by scripts/update_benchmark_resubmission.py</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MTL-PepPred rows (green) = mean of 5 independent runs, seeds 42, 1, 2, 3, 4 (B1). SD (sample, ddof=1) in *_SD columns.</t>
+          <t>MTL-PepPred rows (green) = mean of 5 independent runs, seeds 42, 1, 2, 3, 4. SD (sample, ddof=1) in *_SD columns. Stored at full precision, displayed at 2 dp; Table 4 shows the 2-dp rounding.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All baseline rows are unchanged from 'Benchmark Summary - new.xlsx'.</t>
+          <t>All baseline rows are unchanged from 'Benchmark Summary - new.xlsx', except the UniDL4BioPep antioxidant row, whose values from AUC onwards were shifted by one column in the source and are restored here.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACC, AUC, MCC, Sn read from results/test_results_seed_*.json. Sp and BACC derived exactly from accuracy, precision and recall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PR-AUC (mean of 5 runs, with SD) read from results/C0_seed{42,1,2,3,4}_pertask_metrics.csv (B6, 2026-09-21): AMP-off inference on the seed 1-4 weights, which were never deleted, using sklearn average_precision_score to match the manuscript's own method.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-10-06: the UniDL4BioPep antioxidant row was shifted one column from BACC onward. Du et al. (2023), Briefings in Bioinformatics 24(3) bbad135, Table 2 reports ACC 0.804, Sn 0.810, Sp 0.799, MCC 0.608, AUC 0.872, and does not report PR-AUC. BACC = (Sn+Sp)/2 = 0.8045 is consistent with the reported ACC. The row now reads ACC 80.40, AUC 87.20, PR-AUC blank, BACC 80.45, Sn 81.00, Sp 79.90, MCC 60.80. Consequence: MTL-PepPred is 4.2 AUC points BELOW UniDL4BioPep on antioxidant activity, not 2.6 points above; UniDL4BioPep mean AUC 93.81, mean MCC 78.36, mean PR-AUC 94.38 over 20 tasks. Figure 2 must be regenerated from this sheet.</t>
+          <t>All MTL-PepPred metrics read from results/C0_seed{42,1,2,3,4}_pertask_metrics.csv (AMP-off inference; PR-AUC = average precision).</t>
         </is>
       </c>
     </row>
